--- a/docs/convergence/ICTC_CONVERGENCE_AUTHORITY_ACTIVE.xlsx
+++ b/docs/convergence/ICTC_CONVERGENCE_AUTHORITY_ACTIVE.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACTIVE" sheetId="1" r:id="R11b97ba8aaeb4ceb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GOV_CWA1_BINDING" sheetId="2" r:id="R2ef6465134914b72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACTIVE" sheetId="1" r:id="Ra973cf3781344af6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GOV_CWA1_BINDING" sheetId="2" r:id="R4db04438914b4b2e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -276,7 +276,7 @@
         <x:v>ICTC Convergence Authority</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>A6-UX2 active projection</x:v>
+        <x:v>A6-UX2-MAIN reconciliation projection</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -284,7 +284,7 @@
         <x:v>Projection version</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>v3.10-a6-ux2-prepr-minimal</x:v>
+        <x:v>v3.11-a6-ux2-main-reconciliation</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -292,7 +292,7 @@
         <x:v>Base main SHA</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>190bbe0bc97ea0cef10806b1d4bba8aed043b486</x:v>
+        <x:v>69da13b76355e18bfa80f5ee92cd0067a97b4bc8</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -300,7 +300,7 @@
         <x:v>Latest merged PR</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>#131</x:v>
+        <x:v>#132</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -308,7 +308,7 @@
         <x:v>Current execution</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>A6-UX2</x:v>
+        <x:v>A6-UX2-MAIN</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -324,7 +324,7 @@
         <x:v>Trajectory impact</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
-        <x:v>planned</x:v>
+        <x:v>reconciliation</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -337,10 +337,10 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="7" t="str">
-        <x:v>Runtime contraction</x:v>
+        <x:v>Reconciled fact</x:v>
       </x:c>
       <x:c r="B9" s="7" t="str">
-        <x:v>workspace-chrome-3-3 owns live .topbar + stable footer; business 2.7 chrome causes retired</x:v>
+        <x:v>PR #132 observed merged on main@69da13b76355e18bfa80f5ee92cd0067a97b4bc8</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -348,15 +348,15 @@
         <x:v>E2 antagonists</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>100000 real in-memory source-string mutations; 20 families; 0 survivors</x:v>
+        <x:v>100000 deterministic reconciliation antagonists; 0 survivors</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="7" t="str">
-        <x:v>E3 rail</x:v>
+        <x:v>Exact-main evidence</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
-        <x:v>exact-head Chromium: 1440 / 390 / 320</x:v>
+        <x:v>green-quiescent; 0 failed / 0 queued / 0 in-progress workflow runs observed at audit time</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -364,7 +364,7 @@
         <x:v>Claim boundary</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
-        <x:v>repository/runtime automated evidence only; no E4 or human aesthetic certification</x:v>
+        <x:v>convergence truth only; S4-A6 remains open; no enterprise-candidate, E4 or human certification claim</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -393,7 +393,7 @@
         <x:v>bindingSha256</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>e9910d8de8474e52eba132f9821621d7e8c73c9bed204bf55d1003114c046831</x:v>
+        <x:v>6c0f16e416bdb9e1048cbed7f9f77d01121e1821f4172c1da016927bfa2847e3</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -417,7 +417,7 @@
         <x:v>projectionVersion</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>v3.10-a6-ux2-prepr-minimal</x:v>
+        <x:v>v3.11-a6-ux2-main-reconciliation</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -425,7 +425,7 @@
         <x:v>baseMainSha</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>190bbe0bc97ea0cef10806b1d4bba8aed043b486</x:v>
+        <x:v>69da13b76355e18bfa80f5ee92cd0067a97b4bc8</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -466,6 +466,38 @@
       </x:c>
       <x:c r="B11" s="7" t="str">
         <x:v>artifacts/convergence-authority-receipt.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>latestMergedPr</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>#132|69da13b76355e18bfa80f5ee92cd0067a97b4bc8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>currentExecution</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>A6-UX2-MAIN</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>currentExecutionImpact</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>reconciliation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>parentRemainsOpen</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>true</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/convergence/ICTC_CONVERGENCE_AUTHORITY_ACTIVE.xlsx
+++ b/docs/convergence/ICTC_CONVERGENCE_AUTHORITY_ACTIVE.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACTIVE" sheetId="1" r:id="Ra973cf3781344af6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GOV_CWA1_BINDING" sheetId="2" r:id="R4db04438914b4b2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACTIVE" sheetId="1" r:id="R0a0f0ca386ee4ecb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GOV_CWA1_BINDING" sheetId="2" r:id="R4c542bf53caf491e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -22,21 +22,15 @@
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="2">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF0B1F3A"/>
-      </x:patternFill>
     </x:fill>
   </x:fills>
   <x:borders count="2">
@@ -46,20 +40,18 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="8">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -272,99 +264,99 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="6" t="str">
+      <x:c r="A1" s="4" t="str">
         <x:v>ICTC Convergence Authority</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
-        <x:v>A6-UX2-MAIN reconciliation projection</x:v>
+      <x:c r="B1" s="5" t="str">
+        <x:v>A6-UX3 active projection</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="7" t="str">
+      <x:c r="A2" s="4" t="str">
         <x:v>Projection version</x:v>
       </x:c>
-      <x:c r="B2" s="7" t="str">
-        <x:v>v3.11-a6-ux2-main-reconciliation</x:v>
+      <x:c r="B2" s="5" t="str">
+        <x:v>v3.12-a6-ux3-prepr-minimal</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="7" t="str">
+      <x:c r="A3" s="4" t="str">
         <x:v>Base main SHA</x:v>
       </x:c>
-      <x:c r="B3" s="7" t="str">
-        <x:v>69da13b76355e18bfa80f5ee92cd0067a97b4bc8</x:v>
+      <x:c r="B3" s="5" t="str">
+        <x:v>2f1a2b0c6366620af3976cd8c2eaaec63a86cba5</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="7" t="str">
+      <x:c r="A4" s="4" t="str">
         <x:v>Latest merged PR</x:v>
       </x:c>
-      <x:c r="B4" s="7" t="str">
-        <x:v>#132</x:v>
+      <x:c r="B4" s="5" t="str">
+        <x:v>#133</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="7" t="str">
+      <x:c r="A5" s="4" t="str">
         <x:v>Current execution</x:v>
       </x:c>
-      <x:c r="B5" s="7" t="str">
-        <x:v>A6-UX2-MAIN</x:v>
+      <x:c r="B5" s="5" t="str">
+        <x:v>A6-UX3</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="7" t="str">
+      <x:c r="A6" s="4" t="str">
         <x:v>Parent slice</x:v>
       </x:c>
-      <x:c r="B6" s="7" t="str">
+      <x:c r="B6" s="5" t="str">
         <x:v>S4-A6</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="7" t="str">
+      <x:c r="A7" s="4" t="str">
         <x:v>Trajectory impact</x:v>
       </x:c>
-      <x:c r="B7" s="7" t="str">
-        <x:v>reconciliation</x:v>
+      <x:c r="B7" s="5" t="str">
+        <x:v>planned</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="7" t="str">
+      <x:c r="A8" s="4" t="str">
         <x:v>Next slice</x:v>
       </x:c>
-      <x:c r="B8" s="7" t="str">
+      <x:c r="B8" s="5" t="str">
         <x:v>S4-A6</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="7" t="str">
-        <x:v>Reconciled fact</x:v>
-      </x:c>
-      <x:c r="B9" s="7" t="str">
-        <x:v>PR #132 observed merged on main@69da13b76355e18bfa80f5ee92cd0067a97b4bc8</x:v>
+      <x:c r="A9" s="4" t="str">
+        <x:v>Runtime contraction</x:v>
+      </x:c>
+      <x:c r="B9" s="5" t="str">
+        <x:v>operational local owners; one Comprendi standard; scope editor popup overlay; read-only master-detail understanding; no new business provider</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="7" t="str">
+      <x:c r="A10" s="4" t="str">
         <x:v>E2 antagonists</x:v>
       </x:c>
-      <x:c r="B10" s="7" t="str">
-        <x:v>100000 deterministic reconciliation antagonists; 0 survivors</x:v>
+      <x:c r="B10" s="5" t="str">
+        <x:v>100000 deterministic source/model mutations; 32 families; 0 survivors required</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="7" t="str">
-        <x:v>Exact-main evidence</x:v>
-      </x:c>
-      <x:c r="B11" s="7" t="str">
-        <x:v>green-quiescent; 0 failed / 0 queued / 0 in-progress workflow runs observed at audit time</x:v>
+      <x:c r="A11" s="4" t="str">
+        <x:v>E3 rail</x:v>
+      </x:c>
+      <x:c r="B11" s="5" t="str">
+        <x:v>exact-head Chromium: 1440 / 390 / 320; admin + user role boundary</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="7" t="str">
+      <x:c r="A12" s="4" t="str">
         <x:v>Claim boundary</x:v>
       </x:c>
-      <x:c r="B12" s="7" t="str">
-        <x:v>convergence truth only; S4-A6 remains open; no enterprise-candidate, E4 or human certification claim</x:v>
+      <x:c r="B12" s="5" t="str">
+        <x:v>repository/runtime automated evidence only; parent S4-A6 open; no E4, enterprise-candidate or human certification</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -376,128 +368,96 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="76" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="6" t="str">
-        <x:v>key</x:v>
-      </x:c>
-      <x:c r="B1" s="6" t="str">
-        <x:v>value</x:v>
+      <x:c r="A1" s="4" t="str">
+        <x:v>bindingSha256</x:v>
+      </x:c>
+      <x:c r="B1" s="5" t="str">
+        <x:v>17af456bff97888c4dff64798ea691545652efb17b001dc990071437fca29efd</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="7" t="str">
-        <x:v>bindingSha256</x:v>
-      </x:c>
-      <x:c r="B2" s="7" t="str">
-        <x:v>6c0f16e416bdb9e1048cbed7f9f77d01121e1821f4172c1da016927bfa2847e3</x:v>
+      <x:c r="A2" s="4" t="str">
+        <x:v>schemaVersion</x:v>
+      </x:c>
+      <x:c r="B2" s="5" t="str">
+        <x:v>1.0.0</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="7" t="str">
-        <x:v>schemaVersion</x:v>
-      </x:c>
-      <x:c r="B3" s="7" t="str">
-        <x:v>1.0.0</x:v>
+      <x:c r="A3" s="4" t="str">
+        <x:v>authorityPath</x:v>
+      </x:c>
+      <x:c r="B3" s="5" t="str">
+        <x:v>docs/convergence/convergence-authority.json</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="7" t="str">
-        <x:v>authorityPath</x:v>
-      </x:c>
-      <x:c r="B4" s="7" t="str">
-        <x:v>docs/convergence/convergence-authority.json</x:v>
+      <x:c r="A4" s="4" t="str">
+        <x:v>projectionVersion</x:v>
+      </x:c>
+      <x:c r="B4" s="5" t="str">
+        <x:v>v3.12-a6-ux3-prepr-minimal</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="7" t="str">
-        <x:v>projectionVersion</x:v>
-      </x:c>
-      <x:c r="B5" s="7" t="str">
-        <x:v>v3.11-a6-ux2-main-reconciliation</x:v>
+      <x:c r="A5" s="4" t="str">
+        <x:v>baseMainSha</x:v>
+      </x:c>
+      <x:c r="B5" s="5" t="str">
+        <x:v>2f1a2b0c6366620af3976cd8c2eaaec63a86cba5</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="7" t="str">
-        <x:v>baseMainSha</x:v>
-      </x:c>
-      <x:c r="B6" s="7" t="str">
-        <x:v>69da13b76355e18bfa80f5ee92cd0067a97b4bc8</x:v>
+      <x:c r="A6" s="4" t="str">
+        <x:v>activationId</x:v>
+      </x:c>
+      <x:c r="B6" s="5" t="str">
+        <x:v>GOV-CWA-1</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="7" t="str">
-        <x:v>activationId</x:v>
-      </x:c>
-      <x:c r="B7" s="7" t="str">
-        <x:v>GOV-CWA-1</x:v>
+      <x:c r="A7" s="4" t="str">
+        <x:v>nextSlice</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="str">
+        <x:v>S4-A6</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="7" t="str">
-        <x:v>nextSlice</x:v>
-      </x:c>
-      <x:c r="B8" s="7" t="str">
-        <x:v>S4-A6</x:v>
+      <x:c r="A8" s="4" t="str">
+        <x:v>plannedOrder</x:v>
+      </x:c>
+      <x:c r="B8" s="5" t="str">
+        <x:v>S4-A6|S5-B0|S5-B1|S5-B2</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="7" t="str">
-        <x:v>plannedOrder</x:v>
-      </x:c>
-      <x:c r="B9" s="7" t="str">
-        <x:v>S4-A6|S5-B0|S5-B1|S5-B2</x:v>
+      <x:c r="A9" s="4" t="str">
+        <x:v>trajectoryImpactAllowed</x:v>
+      </x:c>
+      <x:c r="B9" s="5" t="str">
+        <x:v>planned|intentional-deviation|neutral|reconciliation</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="7" t="str">
-        <x:v>trajectoryImpactAllowed</x:v>
-      </x:c>
-      <x:c r="B10" s="7" t="str">
-        <x:v>planned|intentional-deviation|neutral|reconciliation</x:v>
+      <x:c r="A10" s="4" t="str">
+        <x:v>receiptPath</x:v>
+      </x:c>
+      <x:c r="B10" s="5" t="str">
+        <x:v>artifacts/convergence-authority-receipt.json</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="7" t="str">
-        <x:v>receiptPath</x:v>
-      </x:c>
-      <x:c r="B11" s="7" t="str">
-        <x:v>artifacts/convergence-authority-receipt.json</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" t="str">
-        <x:v>latestMergedPr</x:v>
-      </x:c>
-      <x:c r="B12" t="str">
-        <x:v>#132|69da13b76355e18bfa80f5ee92cd0067a97b4bc8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" t="str">
-        <x:v>currentExecution</x:v>
-      </x:c>
-      <x:c r="B13" t="str">
-        <x:v>A6-UX2-MAIN</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="str">
-        <x:v>currentExecutionImpact</x:v>
-      </x:c>
-      <x:c r="B14" t="str">
-        <x:v>reconciliation</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" t="str">
-        <x:v>parentRemainsOpen</x:v>
-      </x:c>
-      <x:c r="B15" t="str">
-        <x:v>true</x:v>
+      <x:c r="A11" s="4" t="str">
+        <x:v>currentSubSlice</x:v>
+      </x:c>
+      <x:c r="B11" s="5" t="str">
+        <x:v>A6-UX3</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/convergence/ICTC_CONVERGENCE_AUTHORITY_ACTIVE.xlsx
+++ b/docs/convergence/ICTC_CONVERGENCE_AUTHORITY_ACTIVE.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACTIVE" sheetId="1" r:id="R0a0f0ca386ee4ecb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GOV_CWA1_BINDING" sheetId="2" r:id="R4c542bf53caf491e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACTIVE_AUTHORITY" sheetId="1" r:id="Rda9e6aedb6164dcd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GOV_CWA1_BINDING" sheetId="2" r:id="Rbe9ac3dc95464675"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,9 +14,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="2">
+  <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
@@ -25,12 +31,17 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="2">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0B1F3A"/>
+      </x:patternFill>
     </x:fill>
   </x:fills>
   <x:borders count="2">
@@ -40,18 +51,28 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="8">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -264,99 +285,75 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="8" t="str">
         <x:v>ICTC Convergence Authority</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
-        <x:v>A6-UX3 active projection</x:v>
+      <x:c r="B1" s="8" t="str">
+        <x:v>A6-UX4 UI/UX Mount</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="4" t="str">
+      <x:c r="A2" s="9" t="str">
+        <x:v>Base main SHA</x:v>
+      </x:c>
+      <x:c r="B2" s="10" t="str">
+        <x:v>04b49c4d09fec3b0ff703a9e74bfd14713993524</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="9" t="str">
+        <x:v>Current execution</x:v>
+      </x:c>
+      <x:c r="B3" s="10" t="str">
+        <x:v>A6-UX4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="9" t="str">
+        <x:v>Parent slice</x:v>
+      </x:c>
+      <x:c r="B4" s="10" t="str">
+        <x:v>S4-A6 (open)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>Next canonical slice</x:v>
+      </x:c>
+      <x:c r="B5" s="10" t="str">
+        <x:v>S4-A6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="9" t="str">
         <x:v>Projection version</x:v>
       </x:c>
-      <x:c r="B2" s="5" t="str">
-        <x:v>v3.12-a6-ux3-prepr-minimal</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="4" t="str">
-        <x:v>Base main SHA</x:v>
-      </x:c>
-      <x:c r="B3" s="5" t="str">
-        <x:v>2f1a2b0c6366620af3976cd8c2eaaec63a86cba5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="4" t="str">
-        <x:v>Latest merged PR</x:v>
-      </x:c>
-      <x:c r="B4" s="5" t="str">
-        <x:v>#133</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="4" t="str">
-        <x:v>Current execution</x:v>
-      </x:c>
-      <x:c r="B5" s="5" t="str">
-        <x:v>A6-UX3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="4" t="str">
-        <x:v>Parent slice</x:v>
-      </x:c>
-      <x:c r="B6" s="5" t="str">
-        <x:v>S4-A6</x:v>
+      <x:c r="B6" s="10" t="str">
+        <x:v>v3.14-a6-ux4-uiux-mount-prepr</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="4" t="str">
-        <x:v>Trajectory impact</x:v>
-      </x:c>
-      <x:c r="B7" s="5" t="str">
-        <x:v>planned</x:v>
+      <x:c r="A7" s="9" t="str">
+        <x:v>Source workbook</x:v>
+      </x:c>
+      <x:c r="B7" s="10" t="str">
+        <x:v>ICTC_CONVERGENCE_AUTHORITY_WORKBOOK_v3.8_GOVERNANCE_ACTIVATION_AUDIT.xlsx</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="4" t="str">
-        <x:v>Next slice</x:v>
-      </x:c>
-      <x:c r="B8" s="5" t="str">
-        <x:v>S4-A6</x:v>
+      <x:c r="A8" s="9" t="str">
+        <x:v>Source workbook SHA-256</x:v>
+      </x:c>
+      <x:c r="B8" s="10" t="str">
+        <x:v>fbc7d2a2681c25a48bfd51e29ec0d2bfbe8aacb0a5c1975a3c1aea541a083a66</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="4" t="str">
-        <x:v>Runtime contraction</x:v>
-      </x:c>
-      <x:c r="B9" s="5" t="str">
-        <x:v>operational local owners; one Comprendi standard; scope editor popup overlay; read-only master-detail understanding; no new business provider</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="4" t="str">
-        <x:v>E2 antagonists</x:v>
-      </x:c>
-      <x:c r="B10" s="5" t="str">
-        <x:v>100000 deterministic source/model mutations; 32 families; 0 survivors required</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="4" t="str">
-        <x:v>E3 rail</x:v>
-      </x:c>
-      <x:c r="B11" s="5" t="str">
-        <x:v>exact-head Chromium: 1440 / 390 / 320; admin + user role boundary</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="4" t="str">
+      <x:c r="A9" s="9" t="str">
         <x:v>Claim boundary</x:v>
       </x:c>
-      <x:c r="B12" s="5" t="str">
-        <x:v>repository/runtime automated evidence only; parent S4-A6 open; no E4, enterprise-candidate or human certification</x:v>
+      <x:c r="B9" s="10" t="str">
+        <x:v>A6-UX4 is a planned semantic UI/UX mounting execution unit inside S4-A6. It compresses duplicate visible collections only when native typed-target binding is exact, fails closed to the canonical worklist otherwise, narrows ambiguous UI claims and hardens standard-browser geometry while preserving business routes and runtime truth. Parent S4-A6 remains open. No enterprise-candidate promotion, enterprise-ready, branch-protection, production-effectiveness, independent-assurance, representative-human usability, accessibility certification or legal/compliance claim is created.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -368,96 +365,112 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="76" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="72" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="8" t="str">
+        <x:v>key</x:v>
+      </x:c>
+      <x:c r="B1" s="8" t="str">
+        <x:v>value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="9" t="str">
         <x:v>bindingSha256</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
-        <x:v>17af456bff97888c4dff64798ea691545652efb17b001dc990071437fca29efd</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="4" t="str">
+      <x:c r="B2" s="10" t="str">
+        <x:v>b0f824f13c46510aae191a563157244dced5667ad8d8dd3425c1c7b95663a47a</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="9" t="str">
         <x:v>schemaVersion</x:v>
       </x:c>
-      <x:c r="B2" s="5" t="str">
+      <x:c r="B3" s="10" t="str">
         <x:v>1.0.0</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="4" t="str">
+    <x:row r="4">
+      <x:c r="A4" s="9" t="str">
         <x:v>authorityPath</x:v>
       </x:c>
-      <x:c r="B3" s="5" t="str">
+      <x:c r="B4" s="10" t="str">
         <x:v>docs/convergence/convergence-authority.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="4" t="str">
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
         <x:v>projectionVersion</x:v>
       </x:c>
-      <x:c r="B4" s="5" t="str">
-        <x:v>v3.12-a6-ux3-prepr-minimal</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="4" t="str">
+      <x:c r="B5" s="10" t="str">
+        <x:v>v3.14-a6-ux4-uiux-mount-prepr</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="9" t="str">
         <x:v>baseMainSha</x:v>
       </x:c>
-      <x:c r="B5" s="5" t="str">
-        <x:v>2f1a2b0c6366620af3976cd8c2eaaec63a86cba5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="4" t="str">
+      <x:c r="B6" s="10" t="str">
+        <x:v>04b49c4d09fec3b0ff703a9e74bfd14713993524</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="9" t="str">
         <x:v>activationId</x:v>
       </x:c>
-      <x:c r="B6" s="5" t="str">
+      <x:c r="B7" s="10" t="str">
         <x:v>GOV-CWA-1</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="4" t="str">
+    <x:row r="8">
+      <x:c r="A8" s="9" t="str">
         <x:v>nextSlice</x:v>
       </x:c>
-      <x:c r="B7" s="5" t="str">
+      <x:c r="B8" s="10" t="str">
         <x:v>S4-A6</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="4" t="str">
+    <x:row r="9">
+      <x:c r="A9" s="9" t="str">
         <x:v>plannedOrder</x:v>
       </x:c>
-      <x:c r="B8" s="5" t="str">
-        <x:v>S4-A6|S5-B0|S5-B1|S5-B2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="4" t="str">
+      <x:c r="B9" s="10" t="str">
+        <x:v>["S4-A6","S5-B0","S5-B1","S5-B2"]</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="9" t="str">
         <x:v>trajectoryImpactAllowed</x:v>
       </x:c>
-      <x:c r="B9" s="5" t="str">
-        <x:v>planned|intentional-deviation|neutral|reconciliation</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="4" t="str">
+      <x:c r="B10" s="10" t="str">
+        <x:v>["planned","intentional-deviation","neutral","reconciliation"]</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="9" t="str">
         <x:v>receiptPath</x:v>
       </x:c>
-      <x:c r="B10" s="5" t="str">
+      <x:c r="B11" s="10" t="str">
         <x:v>artifacts/convergence-authority-receipt.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="4" t="str">
-        <x:v>currentSubSlice</x:v>
-      </x:c>
-      <x:c r="B11" s="5" t="str">
-        <x:v>A6-UX3</x:v>
+    <x:row r="12">
+      <x:c r="A12" s="9" t="str">
+        <x:v>sourceWorkbookSha256</x:v>
+      </x:c>
+      <x:c r="B12" s="10" t="str">
+        <x:v>fbc7d2a2681c25a48bfd51e29ec0d2bfbe8aacb0a5c1975a3c1aea541a083a66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="9" t="str">
+        <x:v>selfReference</x:v>
+      </x:c>
+      <x:c r="B13" s="10" t="str">
+        <x:v>merge SHA is observed only after merge</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/convergence/ICTC_CONVERGENCE_AUTHORITY_ACTIVE.xlsx
+++ b/docs/convergence/ICTC_CONVERGENCE_AUTHORITY_ACTIVE.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACTIVE_AUTHORITY" sheetId="1" r:id="Rda9e6aedb6164dcd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GOV_CWA1_BINDING" sheetId="2" r:id="Rbe9ac3dc95464675"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TRAJECTORY" sheetId="1" r:id="R5222ed88756d418c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GOV_CWA1_BINDING" sheetId="2" r:id="R03e4221a4c654668"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,7 +14,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -28,10 +28,16 @@
     <x:font>
       <x:b/>
       <x:sz val="11"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -43,6 +49,11 @@
         <x:fgColor rgb="FF0B1F3A"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4EEE5"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -51,38 +62,83 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="20">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -280,80 +336,120 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="72" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="66" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="8" t="str">
-        <x:v>ICTC Convergence Authority</x:v>
-      </x:c>
-      <x:c r="B1" s="8" t="str">
-        <x:v>A6-UX4 UI/UX Mount</x:v>
+      <x:c r="A1" s="6" t="str">
+        <x:v>ICTC convergence authority</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>A6-UX4 derived active projection</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="9" t="str">
+      <x:c r="A2" s="11" t="str">
+        <x:v>Projection version</x:v>
+      </x:c>
+      <x:c r="B2" s="14" t="str">
+        <x:v>v3.14-a6-ux4-uiux-mount-prepr</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="11" t="str">
         <x:v>Base main SHA</x:v>
       </x:c>
-      <x:c r="B2" s="10" t="str">
+      <x:c r="B3" s="14" t="str">
         <x:v>04b49c4d09fec3b0ff703a9e74bfd14713993524</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="9" t="str">
+    <x:row r="4">
+      <x:c r="A4" s="11" t="str">
+        <x:v>Observed merged PR</x:v>
+      </x:c>
+      <x:c r="B4" s="14" t="n">
+        <x:v>134</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="11" t="str">
+        <x:v>Current parent</x:v>
+      </x:c>
+      <x:c r="B5" s="14" t="str">
+        <x:v>S4-A6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="11" t="str">
         <x:v>Current execution</x:v>
       </x:c>
-      <x:c r="B3" s="10" t="str">
+      <x:c r="B6" s="14" t="str">
         <x:v>A6-UX4</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="9" t="str">
-        <x:v>Parent slice</x:v>
-      </x:c>
-      <x:c r="B4" s="10" t="str">
-        <x:v>S4-A6 (open)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="9" t="str">
-        <x:v>Next canonical slice</x:v>
-      </x:c>
-      <x:c r="B5" s="10" t="str">
+    <x:row r="7">
+      <x:c r="A7" s="11" t="str">
+        <x:v>Current state</x:v>
+      </x:c>
+      <x:c r="B7" s="14" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="11" t="str">
+        <x:v>Parent remains open</x:v>
+      </x:c>
+      <x:c r="B8" s="15" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="11" t="str">
+        <x:v>Next slice</x:v>
+      </x:c>
+      <x:c r="B9" s="14" t="str">
         <x:v>S4-A6</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="9" t="str">
-        <x:v>Projection version</x:v>
-      </x:c>
-      <x:c r="B6" s="10" t="str">
-        <x:v>v3.14-a6-ux4-uiux-mount-prepr</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="9" t="str">
+    <x:row r="10">
+      <x:c r="A10" s="11" t="str">
+        <x:v>Planned order</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="str">
+        <x:v>S4-A6 &gt; S5-B0 &gt; S5-B1 &gt; S5-B2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="11" t="str">
+        <x:v>Repository bounded stop</x:v>
+      </x:c>
+      <x:c r="B11" s="14" t="str">
+        <x:v>S5-B2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="11" t="str">
+        <x:v>External rail</x:v>
+      </x:c>
+      <x:c r="B12" s="14" t="str">
+        <x:v>E4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="11" t="str">
         <x:v>Source workbook</x:v>
       </x:c>
-      <x:c r="B7" s="10" t="str">
+      <x:c r="B13" s="14" t="str">
         <x:v>ICTC_CONVERGENCE_AUTHORITY_WORKBOOK_v3.8_GOVERNANCE_ACTIVATION_AUDIT.xlsx</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="9" t="str">
-        <x:v>Source workbook SHA-256</x:v>
-      </x:c>
-      <x:c r="B8" s="10" t="str">
+    <x:row r="14">
+      <x:c r="A14" s="11" t="str">
+        <x:v>Source SHA-256</x:v>
+      </x:c>
+      <x:c r="B14" s="14" t="str">
         <x:v>fbc7d2a2681c25a48bfd51e29ec0d2bfbe8aacb0a5c1975a3c1aea541a083a66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="9" t="str">
-        <x:v>Claim boundary</x:v>
-      </x:c>
-      <x:c r="B9" s="10" t="str">
-        <x:v>A6-UX4 is a planned semantic UI/UX mounting execution unit inside S4-A6. It compresses duplicate visible collections only when native typed-target binding is exact, fails closed to the canonical worklist otherwise, narrows ambiguous UI claims and hardens standard-browser geometry while preserving business routes and runtime truth. Parent S4-A6 remains open. No enterprise-candidate promotion, enterprise-ready, branch-protection, production-effectiveness, independent-assurance, representative-human usability, accessibility certification or legal/compliance claim is created.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -365,113 +461,135 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="72" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="8" t="str">
-        <x:v>key</x:v>
-      </x:c>
-      <x:c r="B1" s="8" t="str">
-        <x:v>value</x:v>
+      <x:c r="A1" s="6" t="str">
+        <x:v>bindingField</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>bindingValue</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>checkerMarker</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="9" t="str">
+      <x:c r="A2" s="18" t="str">
+        <x:v>schemaVersion</x:v>
+      </x:c>
+      <x:c r="B2" s="14" t="str">
+        <x:v>1.0.0</x:v>
+      </x:c>
+      <x:c r="C2" s="14" t="str">
+        <x:f>"b0f824f13c46510aae191a563157244dced5667ad8d8dd3425c1c7b95663a47a"</x:f>
+        <x:v>b0f824f13c46510aae191a563157244dced5667ad8d8dd3425c1c7b95663a47a</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="18" t="str">
+        <x:v>authorityPath</x:v>
+      </x:c>
+      <x:c r="B3" s="14" t="str">
+        <x:v>docs/convergence/convergence-authority.json</x:v>
+      </x:c>
+      <x:c r="C3" s="14" t="str">
+        <x:f>"04b49c4d09fec3b0ff703a9e74bfd14713993524"</x:f>
+        <x:v>04b49c4d09fec3b0ff703a9e74bfd14713993524</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="18" t="str">
+        <x:v>projectionVersion</x:v>
+      </x:c>
+      <x:c r="B4" s="14" t="str">
+        <x:v>v3.14-a6-ux4-uiux-mount-prepr</x:v>
+      </x:c>
+      <x:c r="C4" s="14" t="str">
+        <x:f>"GOV-CWA-1"</x:f>
+        <x:v>GOV-CWA-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="18" t="str">
+        <x:v>baseMainSha</x:v>
+      </x:c>
+      <x:c r="B5" s="14" t="str">
+        <x:v>04b49c4d09fec3b0ff703a9e74bfd14713993524</x:v>
+      </x:c>
+      <x:c r="C5" s="14" t="str">
+        <x:f>"S4-A6"</x:f>
+        <x:v>S4-A6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="18" t="str">
+        <x:v>activationId</x:v>
+      </x:c>
+      <x:c r="B6" s="14" t="str">
+        <x:v>GOV-CWA-1</x:v>
+      </x:c>
+      <x:c r="C6" s="14" t="str">
+        <x:f>"trajectoryImpactAllowed"</x:f>
+        <x:v>trajectoryImpactAllowed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="18" t="str">
+        <x:v>nextSlice</x:v>
+      </x:c>
+      <x:c r="B7" s="14" t="str">
+        <x:v>S4-A6</x:v>
+      </x:c>
+      <x:c r="C7" s="14"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="18" t="str">
+        <x:v>plannedOrder</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="str">
+        <x:v>S4-A6 | S5-B0 | S5-B1 | S5-B2</x:v>
+      </x:c>
+      <x:c r="C8" s="14"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="18" t="str">
+        <x:v>trajectoryImpactAllowed</x:v>
+      </x:c>
+      <x:c r="B9" s="14" t="str">
+        <x:v>planned | intentional-deviation | neutral | reconciliation</x:v>
+      </x:c>
+      <x:c r="C9" s="14"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="18" t="str">
+        <x:v>receiptPath</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="str">
+        <x:v>artifacts/convergence-authority-receipt.json</x:v>
+      </x:c>
+      <x:c r="C10" s="14"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="18" t="str">
         <x:v>bindingSha256</x:v>
       </x:c>
-      <x:c r="B2" s="10" t="str">
+      <x:c r="B11" s="14" t="str">
         <x:v>b0f824f13c46510aae191a563157244dced5667ad8d8dd3425c1c7b95663a47a</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="9" t="str">
-        <x:v>schemaVersion</x:v>
-      </x:c>
-      <x:c r="B3" s="10" t="str">
-        <x:v>1.0.0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="9" t="str">
-        <x:v>authorityPath</x:v>
-      </x:c>
-      <x:c r="B4" s="10" t="str">
-        <x:v>docs/convergence/convergence-authority.json</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="9" t="str">
-        <x:v>projectionVersion</x:v>
-      </x:c>
-      <x:c r="B5" s="10" t="str">
-        <x:v>v3.14-a6-ux4-uiux-mount-prepr</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="9" t="str">
-        <x:v>baseMainSha</x:v>
-      </x:c>
-      <x:c r="B6" s="10" t="str">
-        <x:v>04b49c4d09fec3b0ff703a9e74bfd14713993524</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="9" t="str">
-        <x:v>activationId</x:v>
-      </x:c>
-      <x:c r="B7" s="10" t="str">
-        <x:v>GOV-CWA-1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="9" t="str">
-        <x:v>nextSlice</x:v>
-      </x:c>
-      <x:c r="B8" s="10" t="str">
-        <x:v>S4-A6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="9" t="str">
-        <x:v>plannedOrder</x:v>
-      </x:c>
-      <x:c r="B9" s="10" t="str">
-        <x:v>["S4-A6","S5-B0","S5-B1","S5-B2"]</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="9" t="str">
-        <x:v>trajectoryImpactAllowed</x:v>
-      </x:c>
-      <x:c r="B10" s="10" t="str">
-        <x:v>["planned","intentional-deviation","neutral","reconciliation"]</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="9" t="str">
-        <x:v>receiptPath</x:v>
-      </x:c>
-      <x:c r="B11" s="10" t="str">
-        <x:v>artifacts/convergence-authority-receipt.json</x:v>
-      </x:c>
+      <x:c r="C11" s="14"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="9" t="str">
-        <x:v>sourceWorkbookSha256</x:v>
-      </x:c>
-      <x:c r="B12" s="10" t="str">
-        <x:v>fbc7d2a2681c25a48bfd51e29ec0d2bfbe8aacb0a5c1975a3c1aea541a083a66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="9" t="str">
-        <x:v>selfReference</x:v>
-      </x:c>
-      <x:c r="B13" s="10" t="str">
-        <x:v>merge SHA is observed only after merge</x:v>
-      </x:c>
+      <x:c r="A12" s="18" t="str">
+        <x:v>claimBoundary</x:v>
+      </x:c>
+      <x:c r="B12" s="14" t="str">
+        <x:v>Derived repository planning/reconciliation projection only; no prospective merge identifier, enterprise-ready, deployment-effectiveness, branch-protection, independent-assurance or legal/compliance claim.</x:v>
+      </x:c>
+      <x:c r="C12" s="14"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/convergence/ICTC_CONVERGENCE_AUTHORITY_ACTIVE.xlsx
+++ b/docs/convergence/ICTC_CONVERGENCE_AUTHORITY_ACTIVE.xlsx
@@ -2,8 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TRAJECTORY" sheetId="1" r:id="R5222ed88756d418c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GOV_CWA1_BINDING" sheetId="2" r:id="R03e4221a4c654668"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OVERVIEW" sheetId="1" r:id="Rd03fc7a2dc5b46e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHAIN" sheetId="2" r:id="Rdad8fe24004f4378"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WORKSTREAMS" sheetId="3" r:id="R33d27ab438aa4f2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOT" sheetId="4" r:id="Rb797f1026b6b4802"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEBT" sheetId="5" r:id="Rbfef0935246543ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCOPE" sheetId="6" r:id="Rc3db7a472b5c4468"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EXTERNAL" sheetId="7" r:id="R64072c0729024c60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BINDING" sheetId="8" r:id="R040c08b0f3b74b50"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,23 +27,23 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="11"/>
+      <x:sz val="16"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
       <x:color rgb="FF1F2937"/>
       <x:name val="Carlito"/>
     </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:name val="Carlito"/>
-    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -49,11 +55,6 @@
         <x:fgColor rgb="FF0B1F3A"/>
       </x:patternFill>
     </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF4EEE5"/>
-      </x:patternFill>
-    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -62,83 +63,64 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="20">
+  <x:cellXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </x:ext>
-      </x:extLst>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </x:ext>
-      </x:extLst>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </x:ext>
-      </x:extLst>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </x:ext>
-      </x:extLst>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
-</file>
-
-<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
-<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
-  <xfpb:bag type="Checkbox"/>
-  <xfpb:bag type="XFControls">
-    <xfpb:bagId k="CellControl">0</xfpb:bagId>
-  </xfpb:bag>
-  <xfpb:bag type="XFComplement">
-    <xfpb:bagId k="XFControls">1</xfpb:bagId>
-  </xfpb:bag>
-  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
-    <xfpb:a k="MappedFeaturePropertyBags">
-      <xfpb:bagId>2</xfpb:bagId>
-    </xfpb:a>
-  </xfpb:bag>
-</xfpb:FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -336,123 +318,88 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="66" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="70" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="6" t="str">
-        <x:v>ICTC convergence authority</x:v>
-      </x:c>
-      <x:c r="B1" s="6" t="str">
-        <x:v>A6-UX4 derived active projection</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="11" t="str">
-        <x:v>Projection version</x:v>
-      </x:c>
-      <x:c r="B2" s="14" t="str">
-        <x:v>v3.14-a6-ux4-uiux-mount-prepr</x:v>
-      </x:c>
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="5" t="str">
+        <x:v>ICTC Convergence Authority — GOV-WB4</x:v>
+      </x:c>
+      <x:c r="B1" s="5"/>
+      <x:c r="C1" s="5"/>
+      <x:c r="D1" s="5"/>
+      <x:c r="E1" s="5"/>
+      <x:c r="F1" s="5"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="11" t="str">
-        <x:v>Base main SHA</x:v>
-      </x:c>
-      <x:c r="B3" s="14" t="str">
-        <x:v>04b49c4d09fec3b0ff703a9e74bfd14713993524</x:v>
+      <x:c r="A3" s="13" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B3" s="13" t="str">
+        <x:v>Value</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="11" t="str">
-        <x:v>Observed merged PR</x:v>
-      </x:c>
-      <x:c r="B4" s="14" t="n">
-        <x:v>134</x:v>
+      <x:c r="A4" s="20" t="str">
+        <x:v>Base main</x:v>
+      </x:c>
+      <x:c r="B4" s="20" t="str">
+        <x:v>f766fc064b0f8552f4821776755d72b56b757205</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="11" t="str">
-        <x:v>Current parent</x:v>
-      </x:c>
-      <x:c r="B5" s="14" t="str">
-        <x:v>S4-A6</x:v>
+      <x:c r="A5" s="20" t="str">
+        <x:v>Latest merged PR</x:v>
+      </x:c>
+      <x:c r="B5" s="20" t="str">
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="11" t="str">
-        <x:v>Current execution</x:v>
-      </x:c>
-      <x:c r="B6" s="14" t="str">
-        <x:v>A6-UX4</x:v>
+      <x:c r="A6" s="20" t="str">
+        <x:v>Current slice</x:v>
+      </x:c>
+      <x:c r="B6" s="20" t="str">
+        <x:v>GOV-WB4</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="11" t="str">
-        <x:v>Current state</x:v>
-      </x:c>
-      <x:c r="B7" s="14" t="str">
-        <x:v>candidate</x:v>
+      <x:c r="A7" s="20" t="str">
+        <x:v>Next after merge</x:v>
+      </x:c>
+      <x:c r="B7" s="20" t="str">
+        <x:v>TRUTH-0</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="11" t="str">
-        <x:v>Parent remains open</x:v>
-      </x:c>
-      <x:c r="B8" s="15" t="b">
-        <x:v>1</x:v>
+      <x:c r="A8" s="20" t="str">
+        <x:v>S4-A6 parent</x:v>
+      </x:c>
+      <x:c r="B8" s="20" t="str">
+        <x:v>OPEN</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="11" t="str">
-        <x:v>Next slice</x:v>
-      </x:c>
-      <x:c r="B9" s="14" t="str">
-        <x:v>S4-A6</x:v>
+      <x:c r="A9" s="20" t="str">
+        <x:v>Enterprise candidate</x:v>
+      </x:c>
+      <x:c r="B9" s="20" t="str">
+        <x:v>false</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="11" t="str">
-        <x:v>Planned order</x:v>
-      </x:c>
-      <x:c r="B10" s="14" t="str">
-        <x:v>S4-A6 &gt; S5-B0 &gt; S5-B1 &gt; S5-B2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="11" t="str">
-        <x:v>Repository bounded stop</x:v>
-      </x:c>
-      <x:c r="B11" s="14" t="str">
-        <x:v>S5-B2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="11" t="str">
-        <x:v>External rail</x:v>
-      </x:c>
-      <x:c r="B12" s="14" t="str">
-        <x:v>E4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="11" t="str">
-        <x:v>Source workbook</x:v>
-      </x:c>
-      <x:c r="B13" s="14" t="str">
-        <x:v>ICTC_CONVERGENCE_AUTHORITY_WORKBOOK_v3.8_GOVERNANCE_ACTIVATION_AUDIT.xlsx</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="11" t="str">
-        <x:v>Source SHA-256</x:v>
-      </x:c>
-      <x:c r="B14" s="14" t="str">
-        <x:v>fbc7d2a2681c25a48bfd51e29ec0d2bfbe8aacb0a5c1975a3c1aea541a083a66</x:v>
+      <x:c r="A10" s="20" t="str">
+        <x:v>Claim boundary</x:v>
+      </x:c>
+      <x:c r="B10" s="20" t="str">
+        <x:v>Repository sequencing only; external evidence stays external.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:F1"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -461,135 +408,1092 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="72" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="50" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="50" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="6" t="str">
-        <x:v>bindingField</x:v>
-      </x:c>
-      <x:c r="B1" s="6" t="str">
-        <x:v>bindingValue</x:v>
-      </x:c>
-      <x:c r="C1" s="6" t="str">
-        <x:v>checkerMarker</x:v>
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="13" t="str">
+        <x:v>Order</x:v>
+      </x:c>
+      <x:c r="B1" s="13" t="str">
+        <x:v>Slice</x:v>
+      </x:c>
+      <x:c r="C1" s="13" t="str">
+        <x:v>State</x:v>
+      </x:c>
+      <x:c r="D1" s="13" t="str">
+        <x:v>Depends on</x:v>
+      </x:c>
+      <x:c r="E1" s="13" t="str">
+        <x:v>Purpose</x:v>
+      </x:c>
+      <x:c r="F1" s="13" t="str">
+        <x:v>User effect</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="18" t="str">
+      <x:c r="A2" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="20" t="str">
+        <x:v>GOV-WB4</x:v>
+      </x:c>
+      <x:c r="C2" s="20" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="D2" s="20" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="E2" s="20" t="str">
+        <x:v>Deterministic convergence authority/workbook and historical-gate decoupling</x:v>
+      </x:c>
+      <x:c r="F2" s="20" t="str">
+        <x:v>No business UI change; contributors get one explicit development chain.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="20" t="str">
+        <x:v>TRUTH-0</x:v>
+      </x:c>
+      <x:c r="C3" s="20" t="str">
+        <x:v>blocked</x:v>
+      </x:c>
+      <x:c r="D3" s="20" t="str">
+        <x:v>GOV-WB4</x:v>
+      </x:c>
+      <x:c r="E3" s="20" t="str">
+        <x:v>Reconcile capability, gap, debt and documentation truth to post-PR-135 main</x:v>
+      </x:c>
+      <x:c r="F3" s="20" t="str">
+        <x:v>Product claims and repository status stop describing stale pre-135 state.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="20" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="20" t="str">
+        <x:v>SCOPE-0</x:v>
+      </x:c>
+      <x:c r="C4" s="20" t="str">
+        <x:v>blocked</x:v>
+      </x:c>
+      <x:c r="D4" s="20" t="str">
+        <x:v>TRUTH-0</x:v>
+      </x:c>
+      <x:c r="E4" s="20" t="str">
+        <x:v>Define Product Operating Model and context-of-use target envelope</x:v>
+      </x:c>
+      <x:c r="F4" s="20" t="str">
+        <x:v>Future product work is tied to explicit users, deployment, scale and non-goals.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" s="20" t="str">
+        <x:v>REALITY-0</x:v>
+      </x:c>
+      <x:c r="C5" s="20" t="str">
+        <x:v>blocked</x:v>
+      </x:c>
+      <x:c r="D5" s="20" t="str">
+        <x:v>SCOPE-0</x:v>
+      </x:c>
+      <x:c r="E5" s="20" t="str">
+        <x:v>Rehearse the declared target envelope against current architecture and runtime</x:v>
+      </x:c>
+      <x:c r="F5" s="20" t="str">
+        <x:v>Feasibility limits are exposed before architecture is changed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="20" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="20" t="str">
+        <x:v>DECIDE-0</x:v>
+      </x:c>
+      <x:c r="C6" s="20" t="str">
+        <x:v>blocked</x:v>
+      </x:c>
+      <x:c r="D6" s="20" t="str">
+        <x:v>REALITY-0</x:v>
+      </x:c>
+      <x:c r="E6" s="20" t="str">
+        <x:v>Make architecture/product-track decisions from scope plus reality evidence</x:v>
+      </x:c>
+      <x:c r="F6" s="20" t="str">
+        <x:v>Only evidence-backed structural changes enter implementation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B7" s="20" t="str">
+        <x:v>S4-A6-CLOSE</x:v>
+      </x:c>
+      <x:c r="C7" s="20" t="str">
+        <x:v>blocked</x:v>
+      </x:c>
+      <x:c r="D7" s="20" t="str">
+        <x:v>DECIDE-0</x:v>
+      </x:c>
+      <x:c r="E7" s="20" t="str">
+        <x:v>Execute applicable repository workstreams and close GAP-020 only if evidence supports it</x:v>
+      </x:c>
+      <x:c r="F7" s="20" t="str">
+        <x:v>Remaining internal assurance debt is removed without weakening A1-A5/UX1-UX4.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B8" s="20" t="str">
+        <x:v>S5-CANDIDATE-SEAL</x:v>
+      </x:c>
+      <x:c r="C8" s="20" t="str">
+        <x:v>blocked</x:v>
+      </x:c>
+      <x:c r="D8" s="20" t="str">
+        <x:v>S4-A6-CLOSE</x:v>
+      </x:c>
+      <x:c r="E8" s="20" t="str">
+        <x:v>Atomic exact-head enterprise-candidate repository seal</x:v>
+      </x:c>
+      <x:c r="F8" s="20" t="str">
+        <x:v>One exact SHA may be promoted to enterprise-candidate; never to enterprise-ready without external evidence.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="50" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="13" t="str">
+        <x:v>ID</x:v>
+      </x:c>
+      <x:c r="B1" s="13" t="str">
+        <x:v>Workstream</x:v>
+      </x:c>
+      <x:c r="C1" s="13" t="str">
+        <x:v>State</x:v>
+      </x:c>
+      <x:c r="D1" s="13" t="str">
+        <x:v>Safe start after</x:v>
+      </x:c>
+      <x:c r="E1" s="13" t="str">
+        <x:v>Target slice</x:v>
+      </x:c>
+      <x:c r="F1" s="13" t="str">
+        <x:v>Debt refs</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="20" t="str">
+        <x:v>C1</x:v>
+      </x:c>
+      <x:c r="B2" s="20" t="str">
+        <x:v>compatibility responsibility contraction</x:v>
+      </x:c>
+      <x:c r="C2" s="20" t="str">
+        <x:v>todo</x:v>
+      </x:c>
+      <x:c r="D2" s="20" t="str">
+        <x:v>DECIDE-0</x:v>
+      </x:c>
+      <x:c r="E2" s="20" t="str">
+        <x:v>S4-A6-CLOSE</x:v>
+      </x:c>
+      <x:c r="F2" s="20" t="str">
+        <x:v>GAP-020</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="20" t="str">
+        <x:v>C2</x:v>
+      </x:c>
+      <x:c r="B3" s="20" t="str">
+        <x:v>secure delivery provenance/signing repository portion</x:v>
+      </x:c>
+      <x:c r="C3" s="20" t="str">
+        <x:v>todo</x:v>
+      </x:c>
+      <x:c r="D3" s="20" t="str">
+        <x:v>TRUTH-0</x:v>
+      </x:c>
+      <x:c r="E3" s="20" t="str">
+        <x:v>S4-A6-CLOSE</x:v>
+      </x:c>
+      <x:c r="F3" s="20" t="str">
+        <x:v>F-06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="20" t="str">
+        <x:v>C3</x:v>
+      </x:c>
+      <x:c r="B4" s="20" t="str">
+        <x:v>target-sized pagination/capacity contract</x:v>
+      </x:c>
+      <x:c r="C4" s="20" t="str">
+        <x:v>todo</x:v>
+      </x:c>
+      <x:c r="D4" s="20" t="str">
+        <x:v>DECIDE-0</x:v>
+      </x:c>
+      <x:c r="E4" s="20" t="str">
+        <x:v>S4-A6-CLOSE</x:v>
+      </x:c>
+      <x:c r="F4" s="20" t="str">
+        <x:v>F-13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="20" t="str">
+        <x:v>C4</x:v>
+      </x:c>
+      <x:c r="B5" s="20" t="str">
+        <x:v>AI eval/drift/rollback gate</x:v>
+      </x:c>
+      <x:c r="C5" s="20" t="str">
+        <x:v>todo</x:v>
+      </x:c>
+      <x:c r="D5" s="20" t="str">
+        <x:v>DECIDE-0</x:v>
+      </x:c>
+      <x:c r="E5" s="20" t="str">
+        <x:v>S4-A6-CLOSE</x:v>
+      </x:c>
+      <x:c r="F5" s="20" t="str">
+        <x:v>F-15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="20" t="str">
+        <x:v>C5</x:v>
+      </x:c>
+      <x:c r="B6" s="20" t="str">
+        <x:v>semantic-owner compression / no hidden post-render business authority</x:v>
+      </x:c>
+      <x:c r="C6" s="20" t="str">
+        <x:v>todo</x:v>
+      </x:c>
+      <x:c r="D6" s="20" t="str">
+        <x:v>TRUTH-0</x:v>
+      </x:c>
+      <x:c r="E6" s="20" t="str">
+        <x:v>S4-A6-CLOSE</x:v>
+      </x:c>
+      <x:c r="F6" s="20" t="str">
+        <x:v>GAP-020</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="46" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="60" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="13" t="str">
+        <x:v>ID</x:v>
+      </x:c>
+      <x:c r="B1" s="13" t="str">
+        <x:v>Truth topic</x:v>
+      </x:c>
+      <x:c r="C1" s="13" t="str">
+        <x:v>Authority</x:v>
+      </x:c>
+      <x:c r="D1" s="13" t="str">
+        <x:v>Rule</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="20" t="str">
+        <x:v>SOT-GIT</x:v>
+      </x:c>
+      <x:c r="B2" s="20" t="str">
+        <x:v>merge and exact-SHA facts</x:v>
+      </x:c>
+      <x:c r="C2" s="20" t="str">
+        <x:v>Git/GitHub</x:v>
+      </x:c>
+      <x:c r="D2" s="20" t="str">
+        <x:v>Repository files may reference observed facts but cannot predict future merge SHAs.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="20" t="str">
+        <x:v>SOT-PRODUCT</x:v>
+      </x:c>
+      <x:c r="B3" s="20" t="str">
+        <x:v>product intent and boundaries</x:v>
+      </x:c>
+      <x:c r="C3" s="20" t="str">
+        <x:v>docs/PRODUCT.md</x:v>
+      </x:c>
+      <x:c r="D3" s="20" t="str">
+        <x:v>Convergence governance cannot redefine product intent.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="20" t="str">
+        <x:v>SOT-ARCH</x:v>
+      </x:c>
+      <x:c r="B4" s="20" t="str">
+        <x:v>AS-IS architecture</x:v>
+      </x:c>
+      <x:c r="C4" s="20" t="str">
+        <x:v>docs/11_ARCHITECTURE.md</x:v>
+      </x:c>
+      <x:c r="D4" s="20" t="str">
+        <x:v>Planning assumptions cannot overwrite observed architecture.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="20" t="str">
+        <x:v>SOT-RUNTIME</x:v>
+      </x:c>
+      <x:c r="B5" s="20" t="str">
+        <x:v>runtime business behavior</x:v>
+      </x:c>
+      <x:c r="C5" s="20" t="str">
+        <x:v>v3/server.mjs + v3/runtime/* + v3/store.mjs</x:v>
+      </x:c>
+      <x:c r="D5" s="20" t="str">
+        <x:v>Workbook is never runtime business authority.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="20" t="str">
+        <x:v>SOT-CAPABILITY</x:v>
+      </x:c>
+      <x:c r="B6" s="20" t="str">
+        <x:v>repository capability truth</x:v>
+      </x:c>
+      <x:c r="C6" s="20" t="str">
+        <x:v>v3/capability-truth.json</x:v>
+      </x:c>
+      <x:c r="D6" s="20" t="str">
+        <x:v>Repository-proven is distinct from deployment effectiveness.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="20" t="str">
+        <x:v>SOT-GAPS</x:v>
+      </x:c>
+      <x:c r="B7" s="20" t="str">
+        <x:v>gap state</x:v>
+      </x:c>
+      <x:c r="C7" s="20" t="str">
+        <x:v>v3/gaps.json + docs/GAP_REGISTER.md</x:v>
+      </x:c>
+      <x:c r="D7" s="20" t="str">
+        <x:v>Gap closure requires its declared evidence class.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="20" t="str">
+        <x:v>SOT-REMEDIATION</x:v>
+      </x:c>
+      <x:c r="B8" s="20" t="str">
+        <x:v>audit remediation findings</x:v>
+      </x:c>
+      <x:c r="C8" s="20" t="str">
+        <x:v>audit/remediation-registry.json</x:v>
+      </x:c>
+      <x:c r="D8" s="20" t="str">
+        <x:v>E3-E5 findings cannot be self-closed by repository simulation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="20" t="str">
+        <x:v>SOT-CONVERGENCE</x:v>
+      </x:c>
+      <x:c r="B9" s="20" t="str">
+        <x:v>development sequencing and PR reconciliation</x:v>
+      </x:c>
+      <x:c r="C9" s="20" t="str">
+        <x:v>docs/convergence/convergence-authority.json</x:v>
+      </x:c>
+      <x:c r="D9" s="20" t="str">
+        <x:v>This authority sequences work only; it cannot redefine product/runtime/legal truth.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="20" t="str">
+        <x:v>SOT-EXTERNAL</x:v>
+      </x:c>
+      <x:c r="B10" s="20" t="str">
+        <x:v>human, governance and deployment evidence</x:v>
+      </x:c>
+      <x:c r="C10" s="20" t="str">
+        <x:v>observed external systems / independent evidence</x:v>
+      </x:c>
+      <x:c r="D10" s="20" t="str">
+        <x:v>External evidence is referenced, never manufactured by this workbook.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="72" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="13" t="str">
+        <x:v>ID</x:v>
+      </x:c>
+      <x:c r="B1" s="13" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="C1" s="13" t="str">
+        <x:v>Closure class</x:v>
+      </x:c>
+      <x:c r="D1" s="13" t="str">
+        <x:v>Target</x:v>
+      </x:c>
+      <x:c r="E1" s="13" t="str">
+        <x:v>Meaning</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="20" t="str">
+        <x:v>GOV-POST135</x:v>
+      </x:c>
+      <x:c r="B2" s="20" t="str">
+        <x:v>candidate-fixed</x:v>
+      </x:c>
+      <x:c r="C2" s="20" t="str">
+        <x:v>repository-internal</x:v>
+      </x:c>
+      <x:c r="D2" s="20" t="str">
+        <x:v>GOV-WB4</x:v>
+      </x:c>
+      <x:c r="E2" s="20" t="str">
+        <x:v>Convergence authority was anchored to PR #134 although PR #135 is merged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="20" t="str">
+        <x:v>GOV-README-PRESENTATION</x:v>
+      </x:c>
+      <x:c r="B3" s="20" t="str">
+        <x:v>candidate-fixed</x:v>
+      </x:c>
+      <x:c r="C3" s="20" t="str">
+        <x:v>repository-internal</x:v>
+      </x:c>
+      <x:c r="D3" s="20" t="str">
+        <x:v>GOV-WB4</x:v>
+      </x:c>
+      <x:c r="E3" s="20" t="str">
+        <x:v>README still described uiPresentation 3.4 as current while runtime/manifest say local-owners.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="20" t="str">
+        <x:v>GOV-UX3-PLANNING-SHADOW</x:v>
+      </x:c>
+      <x:c r="B4" s="20" t="str">
+        <x:v>candidate-fixed</x:v>
+      </x:c>
+      <x:c r="C4" s="20" t="str">
+        <x:v>repository-internal</x:v>
+      </x:c>
+      <x:c r="D4" s="20" t="str">
+        <x:v>GOV-WB4</x:v>
+      </x:c>
+      <x:c r="E4" s="20" t="str">
+        <x:v>Historical A6-UX3 source oracle still asserted current nextSlice planning tokens.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="20" t="str">
+        <x:v>TRUTH-POST135</x:v>
+      </x:c>
+      <x:c r="B5" s="20" t="str">
+        <x:v>todo</x:v>
+      </x:c>
+      <x:c r="C5" s="20" t="str">
+        <x:v>repository-internal</x:v>
+      </x:c>
+      <x:c r="D5" s="20" t="str">
+        <x:v>TRUTH-0</x:v>
+      </x:c>
+      <x:c r="E5" s="20" t="str">
+        <x:v>capability-truth/gap/docs reconciliation still stops at A5/#128 in multiple current surfaces.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="20" t="str">
+        <x:v>F-06</x:v>
+      </x:c>
+      <x:c r="B6" s="20" t="str">
+        <x:v>in-remediation</x:v>
+      </x:c>
+      <x:c r="C6" s="20" t="str">
+        <x:v>repository-internal</x:v>
+      </x:c>
+      <x:c r="D6" s="20" t="str">
+        <x:v>S4-A6-CLOSE</x:v>
+      </x:c>
+      <x:c r="E6" s="20" t="str">
+        <x:v>Generated SBOM exists; provenance/signature pipeline repository portion remains.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="20" t="str">
+        <x:v>F-13</x:v>
+      </x:c>
+      <x:c r="B7" s="20" t="str">
+        <x:v>open</x:v>
+      </x:c>
+      <x:c r="C7" s="20" t="str">
+        <x:v>repository-internal</x:v>
+      </x:c>
+      <x:c r="D7" s="20" t="str">
+        <x:v>S4-A6-CLOSE</x:v>
+      </x:c>
+      <x:c r="E7" s="20" t="str">
+        <x:v>Versioned pagination/capacity contract remains.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="20" t="str">
+        <x:v>F-15</x:v>
+      </x:c>
+      <x:c r="B8" s="20" t="str">
+        <x:v>in-remediation</x:v>
+      </x:c>
+      <x:c r="C8" s="20" t="str">
+        <x:v>repository-internal</x:v>
+      </x:c>
+      <x:c r="D8" s="20" t="str">
+        <x:v>S4-A6-CLOSE</x:v>
+      </x:c>
+      <x:c r="E8" s="20" t="str">
+        <x:v>AI atomic budget exists; versioned eval/drift/rollback gate remains.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="20" t="str">
+        <x:v>GAP-020</x:v>
+      </x:c>
+      <x:c r="B9" s="20" t="str">
+        <x:v>open</x:v>
+      </x:c>
+      <x:c r="C9" s="20" t="str">
+        <x:v>repository-internal</x:v>
+      </x:c>
+      <x:c r="D9" s="20" t="str">
+        <x:v>S4-A6-CLOSE</x:v>
+      </x:c>
+      <x:c r="E9" s="20" t="str">
+        <x:v>S4 assurance contraction remains open after UX1-UX4.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="20" t="str">
+        <x:v>GAP-021</x:v>
+      </x:c>
+      <x:c r="B10" s="20" t="str">
+        <x:v>open</x:v>
+      </x:c>
+      <x:c r="C10" s="20" t="str">
+        <x:v>repository-internal</x:v>
+      </x:c>
+      <x:c r="D10" s="20" t="str">
+        <x:v>S5-CANDIDATE-SEAL</x:v>
+      </x:c>
+      <x:c r="E10" s="20" t="str">
+        <x:v>Candidate evidence seal remains.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="48" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="13" t="str">
+        <x:v>ID</x:v>
+      </x:c>
+      <x:c r="B1" s="13" t="str">
+        <x:v>Dimension</x:v>
+      </x:c>
+      <x:c r="C1" s="13" t="str">
+        <x:v>State</x:v>
+      </x:c>
+      <x:c r="D1" s="13" t="str">
+        <x:v>Owner slice</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="20" t="str">
+        <x:v>SCOPE-01</x:v>
+      </x:c>
+      <x:c r="B2" s="20" t="str">
+        <x:v>primary operator and buyer</x:v>
+      </x:c>
+      <x:c r="C2" s="20" t="str">
+        <x:v>undefined</x:v>
+      </x:c>
+      <x:c r="D2" s="20" t="str">
+        <x:v>SCOPE-0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="20" t="str">
+        <x:v>SCOPE-02</x:v>
+      </x:c>
+      <x:c r="B3" s="20" t="str">
+        <x:v>must-win jobs</x:v>
+      </x:c>
+      <x:c r="C3" s="20" t="str">
+        <x:v>undefined</x:v>
+      </x:c>
+      <x:c r="D3" s="20" t="str">
+        <x:v>SCOPE-0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="20" t="str">
+        <x:v>SCOPE-03</x:v>
+      </x:c>
+      <x:c r="B4" s="20" t="str">
+        <x:v>seven-process breadth</x:v>
+      </x:c>
+      <x:c r="C4" s="20" t="str">
+        <x:v>undefined</x:v>
+      </x:c>
+      <x:c r="D4" s="20" t="str">
+        <x:v>SCOPE-0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="20" t="str">
+        <x:v>SCOPE-04</x:v>
+      </x:c>
+      <x:c r="B5" s="20" t="str">
+        <x:v>deployment topology</x:v>
+      </x:c>
+      <x:c r="C5" s="20" t="str">
+        <x:v>undefined</x:v>
+      </x:c>
+      <x:c r="D5" s="20" t="str">
+        <x:v>SCOPE-0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="20" t="str">
+        <x:v>SCOPE-05</x:v>
+      </x:c>
+      <x:c r="B6" s="20" t="str">
+        <x:v>scale and concurrency</x:v>
+      </x:c>
+      <x:c r="C6" s="20" t="str">
+        <x:v>undefined</x:v>
+      </x:c>
+      <x:c r="D6" s="20" t="str">
+        <x:v>SCOPE-0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="20" t="str">
+        <x:v>SCOPE-06</x:v>
+      </x:c>
+      <x:c r="B7" s="20" t="str">
+        <x:v>supported clients</x:v>
+      </x:c>
+      <x:c r="C7" s="20" t="str">
+        <x:v>undefined</x:v>
+      </x:c>
+      <x:c r="D7" s="20" t="str">
+        <x:v>SCOPE-0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="20" t="str">
+        <x:v>SCOPE-07</x:v>
+      </x:c>
+      <x:c r="B8" s="20" t="str">
+        <x:v>install/update/rollback support</x:v>
+      </x:c>
+      <x:c r="C8" s="20" t="str">
+        <x:v>undefined</x:v>
+      </x:c>
+      <x:c r="D8" s="20" t="str">
+        <x:v>SCOPE-0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="20" t="str">
+        <x:v>SCOPE-08</x:v>
+      </x:c>
+      <x:c r="B9" s="20" t="str">
+        <x:v>data sensitivity/residency</x:v>
+      </x:c>
+      <x:c r="C9" s="20" t="str">
+        <x:v>undefined</x:v>
+      </x:c>
+      <x:c r="D9" s="20" t="str">
+        <x:v>SCOPE-0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="20" t="str">
+        <x:v>SCOPE-09</x:v>
+      </x:c>
+      <x:c r="B10" s="20" t="str">
+        <x:v>availability/recovery/capacity</x:v>
+      </x:c>
+      <x:c r="C10" s="20" t="str">
+        <x:v>undefined</x:v>
+      </x:c>
+      <x:c r="D10" s="20" t="str">
+        <x:v>SCOPE-0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="20" t="str">
+        <x:v>SCOPE-10</x:v>
+      </x:c>
+      <x:c r="B11" s="20" t="str">
+        <x:v>integrations/master systems</x:v>
+      </x:c>
+      <x:c r="C11" s="20" t="str">
+        <x:v>undefined</x:v>
+      </x:c>
+      <x:c r="D11" s="20" t="str">
+        <x:v>SCOPE-0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="20" t="str">
+        <x:v>SCOPE-11</x:v>
+      </x:c>
+      <x:c r="B12" s="20" t="str">
+        <x:v>roles/delegation/SoD</x:v>
+      </x:c>
+      <x:c r="C12" s="20" t="str">
+        <x:v>undefined</x:v>
+      </x:c>
+      <x:c r="D12" s="20" t="str">
+        <x:v>SCOPE-0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="20" t="str">
+        <x:v>SCOPE-12</x:v>
+      </x:c>
+      <x:c r="B13" s="20" t="str">
+        <x:v>product success metrics</x:v>
+      </x:c>
+      <x:c r="C13" s="20" t="str">
+        <x:v>undefined</x:v>
+      </x:c>
+      <x:c r="D13" s="20" t="str">
+        <x:v>SCOPE-0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="20" t="str">
+        <x:v>SCOPE-13</x:v>
+      </x:c>
+      <x:c r="B14" s="20" t="str">
+        <x:v>feature/architecture budget and non-goals</x:v>
+      </x:c>
+      <x:c r="C14" s="20" t="str">
+        <x:v>undefined</x:v>
+      </x:c>
+      <x:c r="D14" s="20" t="str">
+        <x:v>SCOPE-0</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="80" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="13" t="str">
+        <x:v>Rail</x:v>
+      </x:c>
+      <x:c r="B1" s="13" t="str">
+        <x:v>State</x:v>
+      </x:c>
+      <x:c r="C1" s="13" t="str">
+        <x:v>Evidence item</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="20" t="str">
+        <x:v>E3-HUMAN</x:v>
+      </x:c>
+      <x:c r="B2" s="20" t="str">
+        <x:v>external</x:v>
+      </x:c>
+      <x:c r="C2" s="20" t="str">
+        <x:v>human assistive-technology and usability evidence</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="20" t="str">
+        <x:v>E3-GOV</x:v>
+      </x:c>
+      <x:c r="B3" s="20" t="str">
+        <x:v>external</x:v>
+      </x:c>
+      <x:c r="C3" s="20" t="str">
+        <x:v>server-side protected delivery and required-review enforcement</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="20" t="str">
+        <x:v>E3-GOV</x:v>
+      </x:c>
+      <x:c r="B4" s="20" t="str">
+        <x:v>external</x:v>
+      </x:c>
+      <x:c r="C4" s="20" t="str">
+        <x:v>independent security/review evidence</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="20" t="str">
+        <x:v>E4-DEPLOY</x:v>
+      </x:c>
+      <x:c r="B5" s="20" t="str">
+        <x:v>external</x:v>
+      </x:c>
+      <x:c r="C5" s="20" t="str">
+        <x:v>production scanner efficacy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="20" t="str">
+        <x:v>E4-DEPLOY</x:v>
+      </x:c>
+      <x:c r="B6" s="20" t="str">
+        <x:v>external</x:v>
+      </x:c>
+      <x:c r="C6" s="20" t="str">
+        <x:v>externally managed key custody</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="20" t="str">
+        <x:v>E4-DEPLOY</x:v>
+      </x:c>
+      <x:c r="B7" s="20" t="str">
+        <x:v>external</x:v>
+      </x:c>
+      <x:c r="C7" s="20" t="str">
+        <x:v>approved off-host backup/restore RTO/RPO evidence</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="20" t="str">
+        <x:v>E4-DEPLOY</x:v>
+      </x:c>
+      <x:c r="B8" s="20" t="str">
+        <x:v>external</x:v>
+      </x:c>
+      <x:c r="C8" s="20" t="str">
+        <x:v>production observability/alert drills</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="20" t="str">
+        <x:v>E4-DEPLOY</x:v>
+      </x:c>
+      <x:c r="B9" s="20" t="str">
+        <x:v>external</x:v>
+      </x:c>
+      <x:c r="C9" s="20" t="str">
+        <x:v>signed build provenance verification</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="100" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="13" t="str">
+        <x:v>Key</x:v>
+      </x:c>
+      <x:c r="B1" s="13" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="20" t="str">
         <x:v>schemaVersion</x:v>
       </x:c>
-      <x:c r="B2" s="14" t="str">
-        <x:v>1.0.0</x:v>
-      </x:c>
-      <x:c r="C2" s="14" t="str">
-        <x:f>"b0f824f13c46510aae191a563157244dced5667ad8d8dd3425c1c7b95663a47a"</x:f>
-        <x:v>b0f824f13c46510aae191a563157244dced5667ad8d8dd3425c1c7b95663a47a</x:v>
+      <x:c r="B2" s="20" t="str">
+        <x:v>2.0.0</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="18" t="str">
+      <x:c r="A3" s="20" t="str">
+        <x:v>governanceRevision</x:v>
+      </x:c>
+      <x:c r="B3" s="20" t="str">
+        <x:v>GOV-WB4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="20" t="str">
         <x:v>authorityPath</x:v>
       </x:c>
-      <x:c r="B3" s="14" t="str">
+      <x:c r="B4" s="20" t="str">
         <x:v>docs/convergence/convergence-authority.json</x:v>
       </x:c>
-      <x:c r="C3" s="14" t="str">
-        <x:f>"04b49c4d09fec3b0ff703a9e74bfd14713993524"</x:f>
-        <x:v>04b49c4d09fec3b0ff703a9e74bfd14713993524</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="18" t="str">
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="20" t="str">
         <x:v>projectionVersion</x:v>
       </x:c>
-      <x:c r="B4" s="14" t="str">
-        <x:v>v3.14-a6-ux4-uiux-mount-prepr</x:v>
-      </x:c>
-      <x:c r="C4" s="14" t="str">
-        <x:f>"GOV-CWA-1"</x:f>
-        <x:v>GOV-CWA-1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="18" t="str">
+      <x:c r="B5" s="20" t="str">
+        <x:v>GOV-WB4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="20" t="str">
         <x:v>baseMainSha</x:v>
       </x:c>
-      <x:c r="B5" s="14" t="str">
-        <x:v>04b49c4d09fec3b0ff703a9e74bfd14713993524</x:v>
-      </x:c>
-      <x:c r="C5" s="14" t="str">
-        <x:f>"S4-A6"</x:f>
-        <x:v>S4-A6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="18" t="str">
-        <x:v>activationId</x:v>
-      </x:c>
-      <x:c r="B6" s="14" t="str">
-        <x:v>GOV-CWA-1</x:v>
-      </x:c>
-      <x:c r="C6" s="14" t="str">
-        <x:f>"trajectoryImpactAllowed"</x:f>
-        <x:v>trajectoryImpactAllowed</x:v>
+      <x:c r="B6" s="20" t="str">
+        <x:v>f766fc064b0f8552f4821776755d72b56b757205</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="18" t="str">
-        <x:v>nextSlice</x:v>
-      </x:c>
-      <x:c r="B7" s="14" t="str">
-        <x:v>S4-A6</x:v>
-      </x:c>
-      <x:c r="C7" s="14"/>
+      <x:c r="A7" s="20" t="str">
+        <x:v>currentSlice</x:v>
+      </x:c>
+      <x:c r="B7" s="20" t="str">
+        <x:v>GOV-WB4</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="18" t="str">
-        <x:v>plannedOrder</x:v>
-      </x:c>
-      <x:c r="B8" s="14" t="str">
-        <x:v>S4-A6 | S5-B0 | S5-B1 | S5-B2</x:v>
-      </x:c>
-      <x:c r="C8" s="14"/>
+      <x:c r="A8" s="20" t="str">
+        <x:v>nextAfterMerge</x:v>
+      </x:c>
+      <x:c r="B8" s="20" t="str">
+        <x:v>TRUTH-0</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="18" t="str">
-        <x:v>trajectoryImpactAllowed</x:v>
-      </x:c>
-      <x:c r="B9" s="14" t="str">
-        <x:v>planned | intentional-deviation | neutral | reconciliation</x:v>
-      </x:c>
-      <x:c r="C9" s="14"/>
+      <x:c r="A9" s="20" t="str">
+        <x:v>serialChain</x:v>
+      </x:c>
+      <x:c r="B9" s="20" t="str">
+        <x:v>["GOV-WB4","TRUTH-0","SCOPE-0","REALITY-0","DECIDE-0","S4-A6-CLOSE","S5-CANDIDATE-SEAL"]</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="18" t="str">
+      <x:c r="A10" s="20" t="str">
+        <x:v>sotIds</x:v>
+      </x:c>
+      <x:c r="B10" s="20" t="str">
+        <x:v>["SOT-GIT","SOT-PRODUCT","SOT-ARCH","SOT-RUNTIME","SOT-CAPABILITY","SOT-GAPS","SOT-REMEDIATION","SOT-CONVERGENCE","SOT-EXTERNAL"]</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="20" t="str">
         <x:v>receiptPath</x:v>
       </x:c>
-      <x:c r="B10" s="14" t="str">
+      <x:c r="B11" s="20" t="str">
         <x:v>artifacts/convergence-authority-receipt.json</x:v>
       </x:c>
-      <x:c r="C10" s="14"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="18" t="str">
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="20" t="str">
         <x:v>bindingSha256</x:v>
       </x:c>
-      <x:c r="B11" s="14" t="str">
-        <x:v>b0f824f13c46510aae191a563157244dced5667ad8d8dd3425c1c7b95663a47a</x:v>
-      </x:c>
-      <x:c r="C11" s="14"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="18" t="str">
-        <x:v>claimBoundary</x:v>
-      </x:c>
-      <x:c r="B12" s="14" t="str">
-        <x:v>Derived repository planning/reconciliation projection only; no prospective merge identifier, enterprise-ready, deployment-effectiveness, branch-protection, independent-assurance or legal/compliance claim.</x:v>
-      </x:c>
-      <x:c r="C12" s="14"/>
+      <x:c r="B12" s="20" t="str">
+        <x:v>f823b23e8949926309beb055ad403504bde8c2597498e35ab2a37e2908011812</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="20" t="str">
+        <x:v>projectionClass</x:v>
+      </x:c>
+      <x:c r="B13" s="20" t="str">
+        <x:v>derived-readable-projection</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
